--- a/data/vendor-search/results_all_doorlock.xlsx
+++ b/data/vendor-search/results_all_doorlock.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,8 +477,10 @@
       <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -483,6 +490,11 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>cpe:2.3:a:wireshark:wireshark:1.8.0:*:*:*:*:*:*:*|cpe:2.3:a:wireshark:wireshark:1.8.1:*:*:*:*:*:*:*|cpe:2.3:a:wireshark:wireshark:1.8.2:*:*:*:*:*:*:*|cpe:2.3:a:wireshark:wireshark:1.8.3:*:*:*:*:*:*:*|cpe:2.3:a:wireshark:wireshark:1.8.4:*:*:*:*:*:*:*|cpe:2.3:a:wireshark:wireshark:1.8.5:*:*:*:*:*:*:*|cpe:2.3:a:wireshark:wireshark:1.8.6:*:*:*:*:*:*:*|cpe:2.3:a:wireshark:wireshark:1.8.7:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>assa abloy</t>
         </is>
       </c>
     </row>
@@ -505,8 +517,10 @@
       <c r="D3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E3" t="n">
-        <v>3</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -514,6 +528,11 @@
           <t>cpe:2.3:o:aptus:styra_porttelefonkort_4400_firmware:a1:*:*:*:*:*:*:*|cpe:2.3:h:aptus:styra_porttelefonkort_4400:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>assa abloy</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -534,8 +553,10 @@
       <c r="D4" t="n">
         <v>6.5</v>
       </c>
-      <c r="E4" t="n">
-        <v>3.1</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -545,6 +566,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>cpe:2.3:a:dialog-semiconductor:software_development_kit:*:*:*:*:*:*:*:*|cpe:2.3:h:dialog-semiconductor:da14680:-:*:*:*:*:*:*:*|cpe:2.3:h:dialog-semiconductor:da14681:-:*:*:*:*:*:*:*|cpe:2.3:h:dialog-semiconductor:da14682:-:*:*:*:*:*:*:*|cpe:2.3:h:dialog-semiconductor:da14683:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>august smart lock</t>
         </is>
       </c>
     </row>
@@ -567,8 +593,10 @@
       <c r="D5" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E5" t="n">
-        <v>3.1</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -578,6 +606,11 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>cpe:2.3:o:assaabloy:yale_wipc-301w_firmware:*:*:*:*:*:*:*:*|cpe:2.3:o:assaabloy:yale_wipc-301w_firmware:2.x.2.43:-:*:*:*:*:*:*|cpe:2.3:o:assaabloy:yale_wipc-301w_firmware:2.x.2.43:p1:*:*:*:*:*:*|cpe:2.3:h:assaabloy:yale_wipc-301w:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>assa abloy</t>
         </is>
       </c>
     </row>
@@ -600,8 +633,10 @@
       <c r="D6" t="n">
         <v>6.5</v>
       </c>
-      <c r="E6" t="n">
-        <v>3.1</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -611,6 +646,11 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>cpe:2.3:a:sooil:anydana-a:*:*:*:*:*:*:*:*|cpe:2.3:a:sooil:anydana-i:*:*:*:*:*:*:*:*|cpe:2.3:o:sooil:dana_diabecare_rs_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:sooil:dana_diabecare_rs:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>keypad lock</t>
         </is>
       </c>
     </row>
@@ -633,8 +673,10 @@
       <c r="D7" t="n">
         <v>4.6</v>
       </c>
-      <c r="E7" t="n">
-        <v>3.1</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -644,6 +686,11 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>cpe:2.3:o:etekcity:3-in-1_smart_door_lock_firmware:1.0:*:*:*:*:*:*:*|cpe:2.3:h:etekcity:3-in-1_smart_door_lock:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>smart door lock</t>
         </is>
       </c>
     </row>
@@ -666,8 +713,10 @@
       <c r="D8" t="n">
         <v>2.4</v>
       </c>
-      <c r="E8" t="n">
-        <v>3.1</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -677,6 +726,11 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sulimet:5-in-1_smart_door_lock_firmware:1.0:*:*:*:*:*:*:*|cpe:2.3:h:sulimet:5-in-1_smart_door_lock:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>smart door lock</t>
         </is>
       </c>
     </row>
@@ -699,8 +753,10 @@
       <c r="D9" t="n">
         <v>8.1</v>
       </c>
-      <c r="E9" t="n">
-        <v>3.1</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -710,6 +766,11 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>cpe:2.3:o:u-tec:ultraloq_ul3_bt_firmware:02.27.0012:*:*:*:*:*:*:*|cpe:2.3:h:u-tec:ultraloq_ul3_bt:2nd_gen:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ultraloq</t>
         </is>
       </c>
     </row>
@@ -732,8 +793,10 @@
       <c r="D10" t="n">
         <v>6.8</v>
       </c>
-      <c r="E10" t="n">
-        <v>3.1</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -743,6 +806,11 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>cpe:2.3:o:flient:smart_lock_advanced_firmware:1.0:*:*:*:*:*:*:*|cpe:2.3:h:flient:smart_lock_advanced:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>smart door lock</t>
         </is>
       </c>
     </row>
@@ -765,8 +833,10 @@
       <c r="D11" t="n">
         <v>6.5</v>
       </c>
-      <c r="E11" t="n">
-        <v>3.1</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -776,6 +846,11 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>cpe:2.3:o:flient:smart_lock_advanced_firmware:1.0:*:*:*:*:*:*:*|cpe:2.3:h:flient:smart_lock_advanced:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>smart door lock</t>
         </is>
       </c>
     </row>
@@ -798,8 +873,10 @@
       <c r="D12" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E12" t="n">
-        <v>3.1</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -807,6 +884,11 @@
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>nuki smart</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -827,8 +909,10 @@
       <c r="D13" t="n">
         <v>7.1</v>
       </c>
-      <c r="E13" t="n">
-        <v>3.1</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -836,6 +920,11 @@
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>nuki smart</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -856,8 +945,10 @@
       <c r="D14" t="n">
         <v>6.4</v>
       </c>
-      <c r="E14" t="n">
-        <v>3.1</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -865,6 +956,11 @@
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>nuki smart</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -885,8 +981,10 @@
       <c r="D15" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E15" t="n">
-        <v>3.1</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -894,6 +992,11 @@
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>nuki smart</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -914,8 +1017,10 @@
       <c r="D16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E16" t="n">
-        <v>3.1</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -923,6 +1028,11 @@
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>nuki smart</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -987,8 +1097,10 @@
       <c r="D17" t="n">
         <v>4.7</v>
       </c>
-      <c r="E17" t="n">
-        <v>3.1</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -998,6 +1110,11 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.3:-:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.5:rc1:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.5:rc2:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.5:rc3:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.5:rc4:*:*:*:*:*:*|cpe:2.3:o:linux:linux_kernel:6.5:rc5:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>level lock</t>
         </is>
       </c>
     </row>
@@ -1020,8 +1137,10 @@
       <c r="D18" t="n">
         <v>7.8</v>
       </c>
-      <c r="E18" t="n">
-        <v>3.1</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1031,6 +1150,11 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>cpe:2.3:a:assaabloy:visionline:*:*:*:*:*:*:*:*|cpe:2.3:o:microsoft:windows:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>assa abloy</t>
         </is>
       </c>
     </row>
